--- a/reportes/FCST_vs_Solicitado_S44_2026-10-26.xlsx
+++ b/reportes/FCST_vs_Solicitado_S44_2026-10-26.xlsx
@@ -629,7 +629,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2352,7 +2352,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2388,7 +2388,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2424,7 +2424,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2460,7 +2460,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2496,7 +2496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2568,7 +2568,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2709,7 +2709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2814,7 +2814,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2886,7 +2886,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3024,37 +3024,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Canal Tradicional</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LONCO BASE</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>93.7754</v>
+        <v>137</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>23.844</v>
+        <v>138.24</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>23.712</v>
+        <v>138.24</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.132</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-69.93140000000001</v>
+        <v>1.240000000000009</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.2542671105641778</v>
+        <v>1.009051094890511</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>69.93140000000001</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.005535983895319578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3065,32 +3065,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>LONCO BASE</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>35.4826</v>
+        <v>93.7754</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8.040000000000001</v>
+        <v>23.844</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5.838</v>
+        <v>23.712</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2.082</v>
+        <v>0.132</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-27.4426</v>
+        <v>-69.93140000000001</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.2265899342212803</v>
+        <v>0.2542671105641778</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.4426</v>
+        <v>69.93140000000001</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2589552238805969</v>
+        <v>0.005535983895319578</v>
       </c>
     </row>
     <row r="23">
@@ -3101,32 +3101,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>YOGU YOGU INDIVIDUAL</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>32.0624</v>
+        <v>35.4826</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>12.246</v>
+        <v>8.040000000000001</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.91</v>
+        <v>5.838</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.324</v>
+        <v>2.082</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-19.81639999999999</v>
+        <v>-27.4426</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3819427117121613</v>
+        <v>0.2265899342212803</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>19.81639999999999</v>
+        <v>27.4426</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.02645761881430671</v>
+        <v>0.2589552238805969</v>
       </c>
     </row>
     <row r="24">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
+          <t>YOGU YOGU INDIVIDUAL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>23.032</v>
+        <v>32.0624</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3.732</v>
+        <v>12.246</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.548</v>
+        <v>11.91</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2.184</v>
+        <v>0.324</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-19.3</v>
+        <v>-19.81639999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.1620354289683918</v>
+        <v>0.3819427117121613</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>19.3</v>
+        <v>19.81639999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.5852090032154341</v>
+        <v>0.02645761881430671</v>
       </c>
     </row>
     <row r="25">
@@ -3173,32 +3173,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
+          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>11.623</v>
+        <v>23.032</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4.5894</v>
+        <v>3.732</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3.639</v>
+        <v>1.548</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.9396</v>
+        <v>2.184</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-7.033600000000001</v>
+        <v>-19.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3948550288221629</v>
+        <v>0.1620354289683918</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7.033600000000001</v>
+        <v>19.3</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2047326447901686</v>
+        <v>0.5852090032154341</v>
       </c>
     </row>
     <row r="26">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR FAMILIAR</t>
+          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>11.4065</v>
+        <v>11.623</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3.348</v>
+        <v>4.5894</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2.88</v>
+        <v>3.639</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.468</v>
+        <v>0.9396</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-8.058499999999999</v>
+        <v>-7.033600000000001</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.2935168544251085</v>
+        <v>0.3948550288221629</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8.058499999999999</v>
+        <v>7.033600000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1397849462365592</v>
+        <v>0.2047326447901686</v>
       </c>
     </row>
     <row r="27">
@@ -3245,32 +3245,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO INDIVIDUAL</t>
+          <t>NECTAR WATTS REGULAR FAMILIAR</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10.8505</v>
+        <v>11.4065</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2.298</v>
+        <v>3.348</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.138</v>
+        <v>0.468</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-8.5525</v>
+        <v>-8.058499999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.2117874752315561</v>
+        <v>0.2935168544251085</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8.5525</v>
+        <v>8.058499999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.06005221932114883</v>
+        <v>0.1397849462365592</v>
       </c>
     </row>
     <row r="28">
@@ -3281,32 +3281,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
+          <t>LECHE SABOR LONCO INDIVIDUAL</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7.0262</v>
+        <v>10.8505</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1.518</v>
+        <v>2.298</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.254</v>
+        <v>2.16</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.18</v>
+        <v>0.138</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-5.5082</v>
+        <v>-8.5525</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.2160485041701062</v>
+        <v>0.2117874752315561</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5.5082</v>
+        <v>8.5525</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.1185770750988142</v>
+        <v>0.06005221932114883</v>
       </c>
     </row>
     <row r="29">
@@ -3317,32 +3317,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO FAMILIAR</t>
+          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5.1091</v>
+        <v>7.0262</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1.296</v>
+        <v>1.518</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.164</v>
+        <v>1.254</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-3.813099999999999</v>
+        <v>-5.5082</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.2536650290657846</v>
+        <v>0.2160485041701062</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>3.813099999999999</v>
+        <v>5.5082</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.1185770750988142</v>
       </c>
     </row>
     <row r="30">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MANJAR RETAIL</t>
+          <t>LECHE SABOR LONCO FAMILIAR</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4.8028</v>
+        <v>5.1091</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.7728</v>
+        <v>1.296</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.6072</v>
+        <v>1.164</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.1656</v>
+        <v>0.12</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-4.03</v>
+        <v>-3.813099999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.1609061380861164</v>
+        <v>0.2536650290657846</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4.03</v>
+        <v>3.813099999999999</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.09259259259259259</v>
       </c>
     </row>
     <row r="31">
@@ -3389,32 +3389,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA FAMILIAR</t>
+          <t>MANJAR RETAIL</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>4.7661</v>
+        <v>4.8028</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1.776</v>
+        <v>0.7728</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1.548</v>
+        <v>0.6072</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.228</v>
+        <v>0.1656</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-2.9901</v>
+        <v>-4.03</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3726317114622018</v>
+        <v>0.1609061380861164</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>2.9901</v>
+        <v>4.03</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1283783783783784</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -3425,32 +3425,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK INDIVIDUAL</t>
+          <t>PROTEIN MILK SABORADA FAMILIAR</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4.5966</v>
+        <v>4.7661</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1.611</v>
+        <v>1.776</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1.476</v>
+        <v>1.548</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.135</v>
+        <v>0.228</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-2.9856</v>
+        <v>-2.9901</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3504764391071662</v>
+        <v>0.3726317114622018</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2.9856</v>
+        <v>2.9901</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.08379888268156425</v>
+        <v>0.1283783783783784</v>
       </c>
     </row>
     <row r="33">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CREMA LISTA LONCO</t>
+          <t>LECHE SABOR BREAK INDIVIDUAL</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>4.0323</v>
+        <v>4.5966</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.2985</v>
+        <v>1.611</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.276</v>
+        <v>1.476</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.135</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-3.7338</v>
+        <v>-2.9856</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.07402723011680679</v>
+        <v>0.3504764391071662</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>3.7338</v>
+        <v>2.9856</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.07537688442211053</v>
+        <v>0.08379888268156425</v>
       </c>
     </row>
     <row r="34">
@@ -3497,32 +3497,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LECHE POLVO ENTERA</t>
+          <t>CREMA LISTA LONCO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3.979</v>
+        <v>4.0323</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.9217000000000001</v>
+        <v>0.2985</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.8129</v>
+        <v>0.276</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.1088</v>
+        <v>0.0225</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-3.0573</v>
+        <v>-3.7338</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2316411158582559</v>
+        <v>0.07402723011680679</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3.0573</v>
+        <v>3.7338</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.1180427470977542</v>
+        <v>0.07537688442211053</v>
       </c>
     </row>
     <row r="35">
@@ -3533,32 +3533,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PROTEIN MILK BLANCA FAMILIAR</t>
+          <t>LECHE POLVO ENTERA</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3.5804</v>
+        <v>3.979</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.504</v>
+        <v>0.9217000000000001</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.36</v>
+        <v>0.8129</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.144</v>
+        <v>0.1088</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-3.0764</v>
+        <v>-3.0573</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.1407663948162217</v>
+        <v>0.2316411158582559</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3.0764</v>
+        <v>3.0573</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1180427470977542</v>
       </c>
     </row>
     <row r="36">
@@ -3569,32 +3569,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CREMA BATIR LONCO</t>
+          <t>PROTEIN MILK BLANCA FAMILIAR</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3.1925</v>
+        <v>3.5804</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2.094</v>
+        <v>0.504</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2.058</v>
+        <v>0.36</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.036</v>
+        <v>0.144</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-1.0985</v>
+        <v>-3.0764</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.6559122944400939</v>
+        <v>0.1407663948162217</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>1.0985</v>
+        <v>3.0764</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.0171919770773639</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="37">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHAKE SHAKE INDIVIDUAL</t>
+          <t>CREMA BATIR LONCO</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2.4151</v>
+        <v>3.1925</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.3819</v>
+        <v>2.094</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.342</v>
+        <v>2.058</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.036</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-2.0332</v>
+        <v>-1.0985</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.1581300981325825</v>
+        <v>0.6559122944400939</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2.0332</v>
+        <v>1.0985</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.1044776119402985</v>
+        <v>0.0171919770773639</v>
       </c>
     </row>
     <row r="38">
@@ -3641,32 +3641,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BEBIDA VEGETAL</t>
+          <t>SHAKE SHAKE INDIVIDUAL</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>2.3758</v>
+        <v>2.4151</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.42</v>
+        <v>0.3819</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.384</v>
+        <v>0.342</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0399</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-1.9558</v>
+        <v>-2.0332</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.1767825574543312</v>
+        <v>0.1581300981325825</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1.9558</v>
+        <v>2.0332</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.1044776119402985</v>
       </c>
     </row>
     <row r="39">
@@ -3677,32 +3677,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MOMENTS INDIVIDUAL</t>
+          <t>BEBIDA VEGETAL</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>2.1691</v>
+        <v>2.3758</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.5052000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.138</v>
+        <v>0.384</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.36</v>
+        <v>0.036</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-1.6639</v>
+        <v>-1.9558</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2329076575538242</v>
+        <v>0.1767825574543312</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1.6639</v>
+        <v>1.9558</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.7125890736342041</v>
+        <v>0.08571428571428572</v>
       </c>
     </row>
     <row r="40">
@@ -3713,32 +3713,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NECTAR INDIVIDUAL 0%</t>
+          <t>MOMENTS INDIVIDUAL</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1.9752</v>
+        <v>2.1691</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.246</v>
+        <v>0.5052000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.144</v>
+        <v>0.138</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.078</v>
+        <v>0.36</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-1.7292</v>
+        <v>-1.6639</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.1245443499392467</v>
+        <v>0.2329076575538242</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1.7292</v>
+        <v>1.6639</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.7125890736342041</v>
       </c>
     </row>
     <row r="41">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
+          <t>NECTAR INDIVIDUAL 0%</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1.9081</v>
+        <v>1.9752</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.9239999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.468</v>
+        <v>0.144</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.456</v>
+        <v>0.078</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-0.9841</v>
+        <v>-1.7292</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.4842513495099837</v>
+        <v>0.1245443499392467</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0.9841</v>
+        <v>1.7292</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.4935064935064936</v>
+        <v>0.3170731707317073</v>
       </c>
     </row>
     <row r="42">
@@ -3785,32 +3785,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CREMA LONCO SIN LACTOSA</t>
+          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1.5974</v>
+        <v>1.9081</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.294</v>
+        <v>0.9239999999999999</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.282</v>
+        <v>0.468</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.012</v>
+        <v>0.456</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-1.3034</v>
+        <v>-0.9841</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.1840490797546012</v>
+        <v>0.4842513495099837</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1.3034</v>
+        <v>0.9841</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.04081632653061224</v>
+        <v>0.4935064935064936</v>
       </c>
     </row>
     <row r="43">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MOMENTS FAMILIAR</t>
+          <t>CREMA LONCO SIN LACTOSA</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1.5852</v>
+        <v>1.5974</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.096</v>
+        <v>0.294</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.048</v>
+        <v>0.282</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.048</v>
+        <v>0.012</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-1.4892</v>
+        <v>-1.3034</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.06056018168054505</v>
+        <v>0.1840490797546012</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1.4892</v>
+        <v>1.3034</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.5</v>
+        <v>0.04081632653061224</v>
       </c>
     </row>
     <row r="44">
@@ -3857,32 +3857,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
+          <t>MOMENTS FAMILIAR</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1.4517</v>
+        <v>1.5852</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.24</v>
+        <v>0.096</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.216</v>
+        <v>0.048</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-1.2117</v>
+        <v>-1.4892</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.1653234139284976</v>
+        <v>0.06056018168054505</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1.2117</v>
+        <v>1.4892</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -3893,32 +3893,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YOGU YOGU FAMILIAR</t>
+          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>1.179</v>
+        <v>1.4517</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.252</v>
+        <v>0.24</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.204</v>
+        <v>0.216</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.048</v>
+        <v>0.024</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.927</v>
+        <v>-1.2117</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2137404580152672</v>
+        <v>0.1653234139284976</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0.927</v>
+        <v>1.2117</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
@@ -3929,32 +3929,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MANJAR DOYPACK</t>
+          <t>YOGU YOGU FAMILIAR</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1.131</v>
+        <v>1.179</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.126</v>
+        <v>0.252</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.108</v>
+        <v>0.204</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.018</v>
+        <v>0.048</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-1.005</v>
+        <v>-0.927</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.1114058355437666</v>
+        <v>0.2137404580152672</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1.005</v>
+        <v>0.927</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1904761904761905</v>
       </c>
     </row>
     <row r="47">
@@ -3965,32 +3965,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JUGO 100% 200</t>
+          <t>MANJAR DOYPACK</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1.1197</v>
+        <v>1.131</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.186</v>
+        <v>0.126</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.18</v>
+        <v>0.108</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-0.9337</v>
+        <v>-1.005</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.1661159239081897</v>
+        <v>0.1114058355437666</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.9337</v>
+        <v>1.005</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.03225806451612903</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="48">
@@ -4001,32 +4001,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JUGO 100% 1L</t>
+          <t>JUGO 100% 200</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>-0.9337</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.1661159239081897</v>
+      </c>
+      <c r="I48" s="2" t="n">
         <v>0.9337</v>
       </c>
-      <c r="D48" s="2" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="E48" s="2" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>-0.8976999999999999</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0.03855628146085467</v>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0.8976999999999999</v>
-      </c>
       <c r="J48" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.03225806451612903</v>
       </c>
     </row>
     <row r="49">
@@ -4037,32 +4037,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK FAMILIAR</t>
+          <t>JUGO 100% 1L</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.8180000000000001</v>
+        <v>0.9337</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.156</v>
+        <v>0.036</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.132</v>
+        <v>0.012</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>0.024</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.662</v>
+        <v>-0.8976999999999999</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.1907090464547677</v>
+        <v>0.03855628146085467</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.662</v>
+        <v>0.8976999999999999</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="50">
@@ -4073,32 +4073,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LONCO BASE 200</t>
+          <t>LECHE SABOR BREAK FAMILIAR</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0.7042999999999999</v>
+        <v>0.8180000000000001</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.132</v>
+        <v>0.156</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>0.132</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-0.5722999999999999</v>
+        <v>-0.662</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.1874201334658527</v>
+        <v>0.1907090464547677</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.5722999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
     <row r="51">
@@ -4109,32 +4109,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LECHE POLVO DESCREMADA</t>
+          <t>LONCO BASE 200</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.6836</v>
+        <v>0.7042999999999999</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.3192</v>
+        <v>0.132</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.2736</v>
+        <v>0.132</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-0.3644</v>
+        <v>-0.5722999999999999</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.4669397308367466</v>
+        <v>0.1874201334658527</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0.3644</v>
+        <v>0.5722999999999999</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.1428571428571429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4145,32 +4145,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO SIN LACTOSA</t>
+          <t>LECHE POLVO DESCREMADA</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>0.6034</v>
+        <v>0.6836</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.144</v>
+        <v>0.3192</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.12</v>
+        <v>0.2736</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0456</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-0.4594</v>
+        <v>-0.3644</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2386476632416307</v>
+        <v>0.4669397308367466</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.4594</v>
+        <v>0.3644</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="53">
@@ -4181,32 +4181,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR PROTEINA</t>
+          <t>LECHE EN POLVO SIN LACTOSA</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.5998</v>
+        <v>0.6034</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.0765</v>
+        <v>0.144</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.0765</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-0.5233</v>
+        <v>-0.4594</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.1275425141713905</v>
+        <v>0.2386476632416307</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.5233</v>
+        <v>0.4594</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -4217,32 +4217,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LECHE POLVO SEMIDESCREMADA</t>
+          <t>NECTAR WATTS REGULAR PROTEINA</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.5898</v>
+        <v>0.5998</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.1672</v>
+        <v>0.0765</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1368</v>
+        <v>0.0765</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.0304</v>
+        <v>0</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.4226</v>
+        <v>-0.5233</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2834859274330281</v>
+        <v>0.1275425141713905</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0.4226</v>
+        <v>0.5233</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4253,32 +4253,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FULL PROTEINA BLANCA 1L</t>
+          <t>LECHE POLVO SEMIDESCREMADA</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5898</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.108</v>
+        <v>0.1672</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1368</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0304</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-0.392</v>
+        <v>-0.4226</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.216</v>
+        <v>0.2834859274330281</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0.392</v>
+        <v>0.4226</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="56">
@@ -4289,32 +4289,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NECTAR 115 PROBIOTICOS</t>
+          <t>FULL PROTEINA BLANCA 1L</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.0277</v>
+        <v>0.108</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.0138</v>
+        <v>0.024</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-0.3223</v>
+        <v>-0.392</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.07914285714285714</v>
+        <v>0.216</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.3223</v>
+        <v>0.392</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.4981949458483755</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="57">
@@ -4325,32 +4325,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LECHE EVAPORADA</t>
+          <t>NECTAR 115 PROBIOTICOS</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.2822</v>
+        <v>0.35</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0277</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0138</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.036</v>
+        <v>0.0138</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-0.1982</v>
+        <v>-0.3223</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.297661233167966</v>
+        <v>0.07914285714285714</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.1982</v>
+        <v>0.3223</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4981949458483755</v>
       </c>
     </row>
     <row r="58">
@@ -4361,32 +4361,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
+          <t>LECHE EVAPORADA</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0.233</v>
+        <v>0.2822</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.1818</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.048</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.05120000000000002</v>
+        <v>-0.1982</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.7802575107296137</v>
+        <v>0.297661233167966</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0.05120000000000002</v>
+        <v>0.1982</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="59">
@@ -4397,29 +4397,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
+          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>0.2182</v>
+        <v>0.233</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.0477</v>
+        <v>0.1818</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.0477</v>
+        <v>0.0378</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.1705</v>
+        <v>-0.05120000000000002</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2186067827681026</v>
+        <v>0.7802575107296137</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0.1705</v>
+        <v>0.05120000000000002</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>0</v>
@@ -4433,29 +4433,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ALIMENTO SOJA LIQUIDO</t>
+          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.1622</v>
+        <v>0.2182</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.138</v>
+        <v>0.0477</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.138</v>
+        <v>0.0477</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.0242</v>
+        <v>-0.1705</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.8508014796547473</v>
+        <v>0.2186067827681026</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.0242</v>
+        <v>0.1705</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>0</v>
@@ -4469,29 +4469,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MANJAR</t>
+          <t>ALIMENTO SOJA LIQUIDO</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.1283</v>
+        <v>0.1622</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.138</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.0294</v>
+        <v>0.138</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-0.0989</v>
+        <v>-0.0242</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2291504286827747</v>
+        <v>0.8508014796547473</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0.0989</v>
+        <v>0.0242</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0</v>
@@ -4505,65 +4505,65 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NECTAR 115</t>
+          <t>MANJAR</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>0.115</v>
+        <v>0.1283</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-0.115</v>
+        <v>-0.0989</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0</v>
+        <v>0.2291504286827747</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0.115</v>
+        <v>0.0989</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>Canal Tradicional</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>NECTAR 115</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>137</v>
+        <v>0.115</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>138.24</v>
+        <v>0</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>138.24</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1.240000000000009</v>
+        <v>-0.115</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>1.009051094890511</v>
+        <v>0</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="64">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -14446,7 +14446,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -14740,7 +14740,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -15426,7 +15426,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15475,7 +15475,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15573,7 +15573,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -16161,7 +16161,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16602,7 +16602,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -16979,7 +16979,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -17175,7 +17175,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -17906,7 +17906,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -17955,7 +17955,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18053,7 +18053,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -18099,7 +18099,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18145,7 +18145,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18191,7 +18191,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -18240,7 +18240,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -18286,7 +18286,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -18335,7 +18335,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -18384,7 +18384,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -18430,7 +18430,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -18476,7 +18476,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -18522,7 +18522,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -18571,7 +18571,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -18620,7 +18620,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -18669,7 +18669,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -18718,7 +18718,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -18813,7 +18813,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -18862,7 +18862,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -18908,7 +18908,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -18954,7 +18954,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -19003,7 +19003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -19049,7 +19049,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -19095,7 +19095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -19144,7 +19144,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -19193,7 +19193,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -19242,7 +19242,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -19291,7 +19291,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -19340,7 +19340,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -19389,7 +19389,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -19438,7 +19438,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -19487,7 +19487,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -19533,7 +19533,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -19582,7 +19582,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -19628,7 +19628,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -19674,7 +19674,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -19723,7 +19723,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -19769,7 +19769,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -19818,7 +19818,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -19867,7 +19867,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -19916,7 +19916,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alvi</t>
+          <t>ALVI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19962,7 +19962,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Canal Tradicional</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19972,37 +19972,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ALIMENTO SOJA LIQUIDO</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>30001976</v>
+        <v>30000258</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BEBIDA LONCOLECHE VEGETAL SOYA 6X1LT</t>
+          <t>NECTAR WATTS NJA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.1486</v>
+        <v>93</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.138</v>
+        <v>93.312</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.138</v>
+        <v>93.312</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>-0.0106</v>
+        <v>0.3119999999999976</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.9286675639300135</v>
+        <v>1.003354838709677</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0.0106</v>
+        <v>0</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>0</v>
@@ -20011,7 +20011,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Canal Tradicional</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20021,43 +20021,46 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ALIMENTO SOJA LIQUIDO</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>30001973</v>
+        <v>30002099</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BEBIDA LONCOLECHE AVENA CHOCOLATE 6X1LT</t>
+          <t>NECTAR WATTS TUTTIFLLA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.0136</v>
+        <v>31</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>31.104</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0</v>
+        <v>31.104</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>-0.0136</v>
+        <v>0.1039999999999992</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>1.003354838709677</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0.0136</v>
+        <v>0</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Canal Tradicional</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20067,40 +20070,40 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BEBIDA VEGETAL</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>30001977</v>
+        <v>30000257</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BEBIDA LONCOLECHE VEGETAL ALMENDRA 6X1LT</t>
+          <t>NECTAR WATTS MZNA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1.5214</v>
+        <v>13</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.288</v>
+        <v>13.824</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.282</v>
+        <v>13.824</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>-1.2334</v>
+        <v>0.8239999999999998</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.1892993295648744</v>
+        <v>1.063384615384615</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1.2334</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>0.02083333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -20116,40 +20119,40 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BEBIDA VEGETAL</t>
+          <t>ALIMENTO SOJA LIQUIDO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30000543</v>
+        <v>30001976</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BEBIDA VEGETAL LONCO AVENA LCO 6X1LT</t>
+          <t>BEBIDA LONCOLECHE VEGETAL SOYA 6X1LT</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.8544</v>
+        <v>0.1486</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.102</v>
+        <v>0.138</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>-0.7224</v>
+        <v>-0.0106</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.1544943820224719</v>
+        <v>0.9286675639300135</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.7224</v>
+        <v>0.0106</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.2272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -20165,40 +20168,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CREMA BATIR LONCO</t>
+          <t>ALIMENTO SOJA LIQUIDO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>30000334</v>
+        <v>30001973</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CREMA BATIR LONCO 12X1LT</t>
+          <t>BEBIDA LONCOLECHE AVENA CHOCOLATE 6X1LT</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2.5662</v>
+        <v>0.0136</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1.896</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.884</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>-0.6701999999999999</v>
+        <v>-0.0136</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.7388356324526537</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.6701999999999999</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>0.006329113924050634</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="50">
@@ -20214,40 +20214,40 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CREMA BATIR LONCO</t>
+          <t>BEBIDA VEGETAL</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30001882</v>
+        <v>30001977</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CREMA BATIR LONCO 12X500ML</t>
+          <t>BEBIDA LONCOLECHE VEGETAL ALMENDRA 6X1LT</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.6263</v>
+        <v>1.5214</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.198</v>
+        <v>0.288</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.174</v>
+        <v>0.282</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>-0.4283</v>
+        <v>-1.2334</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.3161424237585822</v>
+        <v>0.1892993295648744</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0.4283</v>
+        <v>1.2334</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.02083333333333334</v>
       </c>
     </row>
     <row r="51">
@@ -20263,40 +20263,40 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CREMA LISTA LONCO</t>
+          <t>BEBIDA VEGETAL</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30000347</v>
+        <v>30000543</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CREMA LISTA LONCO 30X200ML</t>
+          <t>BEBIDA VEGETAL LONCO AVENA LCO 6X1LT</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>3.8641</v>
+        <v>0.8544</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.276</v>
+        <v>0.132</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.276</v>
+        <v>0.102</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>-3.5881</v>
+        <v>-0.7224</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.07142672291089776</v>
+        <v>0.1544943820224719</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3.5881</v>
+        <v>0.7224</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0</v>
+        <v>0.2272727272727273</v>
       </c>
     </row>
     <row r="52">
@@ -20312,40 +20312,40 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CREMA LISTA LONCO</t>
+          <t>CREMA BATIR LONCO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30001716</v>
+        <v>30000334</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CREMA LISTA LONCO 18X250ML</t>
+          <t>CREMA BATIR LONCO 12X1LT</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.1682</v>
+        <v>2.5662</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>0.0225</v>
+        <v>1.896</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
+        <v>1.884</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0.0225</v>
+        <v>0.012</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-0.1457</v>
+        <v>-0.6701999999999999</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.133769322235434</v>
+        <v>0.7388356324526537</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0.1457</v>
+        <v>0.6701999999999999</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>1</v>
+        <v>0.006329113924050634</v>
       </c>
     </row>
     <row r="53">
@@ -20361,40 +20361,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CREMA LONCO SIN LACTOSA</t>
+          <t>CREMA BATIR LONCO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>30000384</v>
+        <v>30001882</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CREMA S/LAC LONCO 30X200ML</t>
+          <t>CREMA BATIR LONCO 12X500ML</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1.3378</v>
+        <v>0.6263</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>0.228</v>
+        <v>0.198</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.216</v>
+        <v>0.174</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0.012</v>
+        <v>0.024</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-1.1098</v>
+        <v>-0.4283</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.1704290626401555</v>
+        <v>0.3161424237585822</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1.1098</v>
+        <v>0.4283</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1212121212121212</v>
       </c>
     </row>
     <row r="54">
@@ -20410,37 +20410,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CREMA LONCO SIN LACTOSA</t>
+          <t>CREMA LISTA LONCO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30000383</v>
+        <v>30000347</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CREMA S/LACT LONCOLECHE 12X1LT</t>
+          <t>CREMA LISTA LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.1567</v>
+        <v>3.8641</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.036</v>
+        <v>0.276</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.036</v>
+        <v>0.276</v>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>-0.1207</v>
+        <v>-3.5881</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.2297383535417996</v>
+        <v>0.07142672291089776</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0.1207</v>
+        <v>3.5881</v>
       </c>
       <c r="M54" s="3" t="n">
         <v>0</v>
@@ -20459,40 +20459,40 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CREMA LONCO SIN LACTOSA</t>
+          <t>CREMA LISTA LONCO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>30002269</v>
+        <v>30001716</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CREMA S/LAC LONCO 500ML</t>
+          <t>CREMA LISTA LONCO 18X250ML</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.1029</v>
+        <v>0.1682</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.03</v>
+        <v>0.0225</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>0.0225</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1457</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.2915451895043731</v>
+        <v>0.133769322235434</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1457</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -20508,40 +20508,40 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FULL PROTEINA BLANCA 1L</t>
+          <t>CREMA LONCO SIN LACTOSA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30002315</v>
+        <v>30000384</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LECHE LONCO FULL PRO DESCR 12X1LT</t>
+          <t>CREMA S/LAC LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.5</v>
+        <v>1.3378</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.108</v>
+        <v>0.228</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0.024</v>
+        <v>0.012</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-0.392</v>
+        <v>-1.1098</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.216</v>
+        <v>0.1704290626401555</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0.392</v>
+        <v>1.1098</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="57">
@@ -20557,40 +20557,40 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>JUGO 100% 1L</t>
+          <t>CREMA LONCO SIN LACTOSA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>30001924</v>
+        <v>30000383</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JUGO 100% WATTS NRJA MIX LV 12X1LT</t>
+          <t>CREMA S/LACT LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.6211</v>
+        <v>0.1567</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.024</v>
+        <v>0.036</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>-0.5971</v>
+        <v>-0.1207</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.03864112059249718</v>
+        <v>0.2297383535417996</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0.5971</v>
+        <v>0.1207</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -20606,37 +20606,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JUGO 100% 1L</t>
+          <t>CREMA LONCO SIN LACTOSA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>30001776</v>
+        <v>30002269</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JUGO 100% WATTS MZNA LV 12X1LT</t>
+          <t>CREMA S/LAC LONCO 500ML</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.3126</v>
+        <v>0.1029</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>-0.3006</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.03838771593090212</v>
+        <v>0.2915451895043731</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0.3006</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>0</v>
@@ -20655,40 +20655,40 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JUGO 100% 200</t>
+          <t>FULL PROTEINA BLANCA 1L</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>30001923</v>
+        <v>30002315</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JUGO 100% WATTS NRJA-MZNA LV 30X200ML</t>
+          <t>LECHE LONCO FULL PRO DESCR 12X1LT</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.4321</v>
+        <v>0.5</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.048</v>
+        <v>0.108</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.048</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>-0.3841</v>
+        <v>-0.392</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.111085396898866</v>
+        <v>0.216</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0.3841</v>
+        <v>0.392</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="60">
@@ -20704,40 +20704,40 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JUGO 100% 200</t>
+          <t>JUGO 100% 1L</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30001487</v>
+        <v>30001924</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JUGO 100% WATTS MZNA LV 30X200ML</t>
+          <t>JUGO 100% WATTS NRJA MIX LV 12X1LT</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.4071</v>
+        <v>0.6211</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.096</v>
+        <v>0.024</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0.006</v>
+        <v>0.024</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>-0.3111</v>
+        <v>-0.5971</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.2358142962417097</v>
+        <v>0.03864112059249718</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0.3111</v>
+        <v>0.5971</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -20753,37 +20753,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JUGO 100% 200</t>
+          <t>JUGO 100% 1L</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>30002292</v>
+        <v>30001776</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JUGO 100% WATTS TUTTI-MANGO LV 30X200ML</t>
+          <t>JUGO 100% WATTS MZNA LV 12X1LT</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.2805</v>
+        <v>0.3126</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.042</v>
+        <v>0.012</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.042</v>
+        <v>0.012</v>
       </c>
       <c r="I61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>-0.2385</v>
+        <v>-0.3006</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.1497326203208556</v>
+        <v>0.03838771593090212</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0.2385</v>
+        <v>0.3006</v>
       </c>
       <c r="M61" s="3" t="n">
         <v>0</v>
@@ -20802,40 +20802,40 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
+          <t>JUGO 100% 200</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30000326</v>
+        <v>30001923</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>LECHE LONCO SEMIDESCREMADA S/LACT 12X1LT</t>
+          <t>JUGO 100% WATTS NRJA-MZNA LV 30X200ML</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>7.972</v>
+        <v>0.4321</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.512</v>
+        <v>0.048</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.42</v>
+        <v>0.048</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1.092</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>-6.460000000000001</v>
+        <v>-0.3841</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.1896638233818364</v>
+        <v>0.111085396898866</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>6.460000000000001</v>
+        <v>0.3841</v>
       </c>
       <c r="M62" s="3" t="n">
-        <v>0.7222222222222223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -20851,40 +20851,40 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
+          <t>JUGO 100% 200</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>30000325</v>
+        <v>30001487</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LECHE  LONCO ENTERA S/LAC NAT 12X1LT</t>
+          <t>JUGO 100% WATTS MZNA LV 30X200ML</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>7.463</v>
+        <v>0.4071</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.792</v>
+        <v>0.096</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.708</v>
+        <v>0.09</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-6.671</v>
+        <v>-0.3111</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.1061235428112019</v>
+        <v>0.2358142962417097</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>6.671</v>
+        <v>0.3111</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>0.1060606060606061</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="64">
@@ -20900,40 +20900,40 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
+          <t>JUGO 100% 200</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>30000353</v>
+        <v>30002292</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LECHE LONCO DESC S/LACTOSA 12X1LT</t>
+          <t>JUGO 100% WATTS TUTTI-MANGO LV 30X200ML</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>6.8474</v>
+        <v>0.2805</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.38</v>
+        <v>0.042</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.372</v>
+        <v>0.042</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1.008</v>
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-5.4674</v>
+        <v>-0.2385</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.2015363495633379</v>
+        <v>0.1497326203208556</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>5.4674</v>
+        <v>0.2385</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0.7304347826086958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -20953,36 +20953,36 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>30000360</v>
+        <v>30000326</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LECHE S/LACT EXTRA CALCIO 12X1LT</t>
+          <t>LECHE LONCO SEMIDESCREMADA S/LACT 12X1LT</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.7496</v>
+        <v>7.972</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.048</v>
+        <v>1.512</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.048</v>
+        <v>0.42</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>1.092</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-0.7016</v>
+        <v>-6.460000000000001</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.06403415154749199</v>
+        <v>0.1896638233818364</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0.7016</v>
+        <v>6.460000000000001</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>0</v>
+        <v>0.7222222222222223</v>
       </c>
     </row>
     <row r="66">
@@ -20998,40 +20998,40 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
+          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30001665</v>
+        <v>30000325</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LECHE POLVO EXTRA CALCIO LONCO 10X800GR</t>
+          <t>LECHE  LONCO ENTERA S/LAC NAT 12X1LT</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.1834</v>
+        <v>7.463</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>0.04</v>
+        <v>0.792</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.04</v>
+        <v>0.708</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-0.1434</v>
+        <v>-6.671</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.2181025081788441</v>
+        <v>0.1061235428112019</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0.1434</v>
+        <v>6.671</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>0</v>
+        <v>0.1060606060606061</v>
       </c>
     </row>
     <row r="67">
@@ -21047,40 +21047,40 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
+          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>30000542</v>
+        <v>30000353</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LECHE POLVO LONCO PROTEIN 14X550GR</t>
+          <t>LECHE LONCO DESC S/LACTOSA 12X1LT</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.0348</v>
+        <v>6.8474</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.0077</v>
+        <v>1.38</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.0077</v>
+        <v>0.372</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
+        <v>1.008</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-0.0271</v>
+        <v>-5.4674</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.221264367816092</v>
+        <v>0.2015363495633379</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0.0271</v>
+        <v>5.4674</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.7304347826086958</v>
       </c>
     </row>
     <row r="68">
@@ -21096,37 +21096,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
+          <t>LECHE BLANCA SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30002276</v>
+        <v>30000360</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LECHE POLVO CALO CRECER 4+ 10X720GR</t>
+          <t>LECHE S/LACT EXTRA CALCIO 12X1LT</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.0864</v>
+        <v>0.7496</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.048</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.0144</v>
+        <v>0.048</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.7016</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.06403415154749199</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.7016</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0</v>
@@ -21145,37 +21145,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
+          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30002273</v>
+        <v>30001665</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LECHE POLVO CALO CRECER 1+ 10X720GR</t>
+          <t>LECHE POLVO EXTRA CALCIO LONCO 10X800GR</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.1834</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.04</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.04</v>
       </c>
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-0.07440000000000001</v>
+        <v>-0.1434</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.08823529411764705</v>
+        <v>0.2181025081788441</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.1434</v>
       </c>
       <c r="M69" s="3" t="n">
         <v>0</v>
@@ -21194,37 +21194,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
+          <t>LECHE EN POLVO ESPECIAL ADULTO</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30002274</v>
+        <v>30000542</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LECHE POLVO CALO CRECER+1 BOLSA 6X1,35KG</t>
+          <t>LECHE POLVO LONCO PROTEIN 14X550GR</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.065</v>
+        <v>0.0348</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0077</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.0162</v>
+        <v>0.0077</v>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-0.0488</v>
+        <v>-0.0271</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.2492307692307692</v>
+        <v>0.221264367816092</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0.0488</v>
+        <v>0.0271</v>
       </c>
       <c r="M70" s="3" t="n">
         <v>0</v>
@@ -21247,30 +21247,33 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>30000395</v>
+        <v>30002276</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LP CALO CRECER 4+ 10X800GR</t>
+          <t>LECHE POLVO CALO CRECER 4+ 10X720GR</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0</v>
+        <v>0.0864</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.144</v>
+        <v>0.0144</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0</v>
+        <v>0.0144</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.144</v>
+        <v>-0.07200000000000001</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.1666666666666667</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>0</v>
@@ -21289,40 +21292,40 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO SIN LACTOSA</t>
+          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>30000321</v>
+        <v>30002273</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LECHE POLVO LONCO S/LACT 10X800GR</t>
+          <t>LECHE POLVO CALO CRECER 1+ 10X720GR</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0.6034</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.144</v>
+        <v>0.0072</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.12</v>
+        <v>0.0072</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-0.4594</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.2386476632416307</v>
+        <v>0.08823529411764705</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0.4594</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -21338,40 +21341,40 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LECHE EVAPORADA</t>
+          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30001149</v>
+        <v>30002274</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LECHE EVAPORADA S/LAC LONCO 30X200ML</t>
+          <t>LECHE POLVO CALO CRECER+1 BOLSA 6X1,35KG</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0.2822</v>
+        <v>0.065</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0162</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0162</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-0.1982</v>
+        <v>-0.0488</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.297661233167966</v>
+        <v>0.2492307692307692</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0.1982</v>
+        <v>0.0488</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -21387,40 +21390,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LECHE POLVO DESCREMADA</t>
+          <t>LECHE EN POLVO ESPECIAL INFANTIL</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30001895</v>
+        <v>30000395</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LECHE POLVO LONCO DESCREMADA 20X760GR</t>
+          <t>LP CALO CRECER 4+ 10X800GR</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.6836</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.3192</v>
+        <v>0.144</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.2736</v>
+        <v>0</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-0.3644</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>0.4669397308367466</v>
+        <v>0.144</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0.3644</v>
+        <v>0</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>0.1428571428571429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -21436,40 +21436,40 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LECHE POLVO ENTERA</t>
+          <t>LECHE EN POLVO SIN LACTOSA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>30001409</v>
+        <v>30000321</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LECHE POLVO CALO ENTERA INST 20X850GR</t>
+          <t>LECHE POLVO LONCO S/LACT 10X800GR</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>2.7196</v>
+        <v>0.6034</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>0.187</v>
+        <v>0.144</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.024</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>-2.5326</v>
+        <v>-0.4594</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.06876011178114429</v>
+        <v>0.2386476632416307</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2.5326</v>
+        <v>0.4594</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="76">
@@ -21485,40 +21485,40 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LECHE POLVO ENTERA</t>
+          <t>LECHE EVAPORADA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>30001410</v>
+        <v>30001149</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LECHE POLVO CALO ENTERA INST 6X1,440KG</t>
+          <t>LECHE EVAPORADA S/LAC LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.9537</v>
+        <v>0.2822</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.6653</v>
+        <v>0.048</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0.0086</v>
+        <v>0.036</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>-0.2797999999999999</v>
+        <v>-0.1982</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.7066163363741219</v>
+        <v>0.297661233167966</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0.2797999999999999</v>
+        <v>0.1982</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.01276153732007716</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="77">
@@ -21534,40 +21534,40 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LECHE POLVO ENTERA</t>
+          <t>LECHE POLVO DESCREMADA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30002125</v>
+        <v>30001895</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LECHE EN POLVO ENTERA LONCO 20X760GR</t>
+          <t>LECHE POLVO LONCO DESCREMADA 20X760GR</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.3057</v>
+        <v>0.6836</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>0.0608</v>
+        <v>0.3192</v>
       </c>
       <c r="H77" s="2" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="I77" s="2" t="n">
         <v>0.0456</v>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0.0152</v>
-      </c>
       <c r="J77" s="2" t="n">
-        <v>-0.2449</v>
+        <v>-0.3644</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.1988877984952568</v>
+        <v>0.4669397308367466</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0.2449</v>
+        <v>0.3644</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571429</v>
       </c>
     </row>
     <row r="78">
@@ -21583,40 +21583,40 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LECHE POLVO SEMIDESCREMADA</t>
+          <t>LECHE POLVO ENTERA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30001715</v>
+        <v>30001409</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LECHE POLVO LONCO SEMIDESCREMADA10X760GR</t>
+          <t>LECHE POLVO CALO ENTERA INST 20X850GR</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.5898</v>
+        <v>2.7196</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.1672</v>
+        <v>0.187</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.1368</v>
+        <v>0.102</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>0.0304</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-0.4226</v>
+        <v>-2.5326</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.2834859274330281</v>
+        <v>0.06876011178114429</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0.4226</v>
+        <v>2.5326</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.4545454545454546</v>
       </c>
     </row>
     <row r="79">
@@ -21632,40 +21632,40 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK FAMILIAR</t>
+          <t>LECHE POLVO ENTERA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>30000478</v>
+        <v>30001410</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CAPPUCCINO LONCOLECHE 12X1LT</t>
+          <t>LECHE POLVO CALO ENTERA INST 6X1,440KG</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.5061</v>
+        <v>0.9537</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.12</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.096</v>
+        <v>0.6653</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0086</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-0.3861</v>
+        <v>-0.2797999999999999</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.2371072910491998</v>
+        <v>0.7066163363741219</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0.3861</v>
+        <v>0.2797999999999999</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0.2</v>
+        <v>0.01276153732007716</v>
       </c>
     </row>
     <row r="80">
@@ -21681,37 +21681,40 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK FAMILIAR</t>
+          <t>LECHE POLVO ENTERA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30000479</v>
+        <v>30002125</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LECHE CHOCO AVELLANAS LONCO 12X1LT</t>
+          <t>LECHE EN POLVO ENTERA LONCO 20X760GR</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.1598</v>
+        <v>0.3057</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>0.0152</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-0.1598</v>
+        <v>-0.2449</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0</v>
+        <v>0.1988877984952568</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0.1598</v>
+        <v>0.2449</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="81">
@@ -21727,40 +21730,40 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK FAMILIAR</t>
+          <t>LECHE POLVO SEMIDESCREMADA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30001992</v>
+        <v>30001715</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>LECHE LONCOLECHE BREAK CARAMEL 12X1LT</t>
+          <t>LECHE POLVO LONCO SEMIDESCREMADA10X760GR</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.1521</v>
+        <v>0.5898</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.036</v>
+        <v>0.1672</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.036</v>
+        <v>0.1368</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>-0.1161</v>
+        <v>-0.4226</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>0.2366863905325443</v>
+        <v>0.2834859274330281</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0.1161</v>
+        <v>0.4226</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="82">
@@ -21776,40 +21779,40 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK INDIVIDUAL</t>
+          <t>LECHE SABOR BREAK FAMILIAR</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>30001404</v>
+        <v>30000478</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>LECHE BREAK CAPPUCCINO LONCO 18X250ML</t>
+          <t>CAPPUCCINO LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>2.8533</v>
+        <v>0.5061</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.9855</v>
+        <v>0.12</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.945</v>
+        <v>0.096</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.024</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>-1.8678</v>
+        <v>-0.3861</v>
       </c>
       <c r="K82" s="3" t="n">
-        <v>0.3453895489433288</v>
+        <v>0.2371072910491998</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1.8678</v>
+        <v>0.3861</v>
       </c>
       <c r="M82" s="3" t="n">
-        <v>0.0410958904109589</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="83">
@@ -21825,40 +21828,37 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK INDIVIDUAL</t>
+          <t>LECHE SABOR BREAK FAMILIAR</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>30001405</v>
+        <v>30000479</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>LECHE BREAK CARAMEL LONCO 18X250ML</t>
+          <t>LECHE CHOCO AVELLANAS LONCO 12X1LT</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.8905</v>
+        <v>0.1598</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>0.378</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.3465</v>
+        <v>0</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>0.0315</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-0.5125</v>
+        <v>-0.1598</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0.4244806288601909</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0.5125</v>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.1598</v>
       </c>
     </row>
     <row r="84">
@@ -21874,40 +21874,40 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LECHE SABOR BREAK INDIVIDUAL</t>
+          <t>LECHE SABOR BREAK FAMILIAR</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30001407</v>
+        <v>30001992</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>LECHE BREAK CHOCO AVELLANA LONCO18X250ML</t>
+          <t>LECHE LONCOLECHE BREAK CARAMEL 12X1LT</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.8528</v>
+        <v>0.1521</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.2475</v>
+        <v>0.036</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.1845</v>
+        <v>0.036</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.1161</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.2902204502814259</v>
+        <v>0.2366863905325443</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.1161</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>0.2545454545454546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -21923,40 +21923,40 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO FAMILIAR</t>
+          <t>LECHE SABOR BREAK INDIVIDUAL</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30002065</v>
+        <v>30001404</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>LECHE CHOCOLATE LONCOLECHE 12X1LT</t>
+          <t>LECHE BREAK CAPPUCCINO LONCO 18X250ML</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>2.5934</v>
+        <v>2.8533</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.732</v>
+        <v>0.9855</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.708</v>
+        <v>0.945</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>0.012</v>
+        <v>0.0405</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>-1.8614</v>
+        <v>-1.8678</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.2822549548854785</v>
+        <v>0.3453895489433288</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1.8614</v>
+        <v>1.8678</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.01639344262295082</v>
+        <v>0.0410958904109589</v>
       </c>
     </row>
     <row r="86">
@@ -21972,37 +21972,40 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO FAMILIAR</t>
+          <t>LECHE SABOR BREAK INDIVIDUAL</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30002076</v>
+        <v>30001405</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LECHE DESC LIGHT CHOC LONCOLECHE 12X1LT</t>
+          <t>LECHE BREAK CARAMEL LONCO 18X250ML</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.7845</v>
+        <v>0.8905</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0</v>
+        <v>0.3465</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>0.0315</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>-0.7845</v>
+        <v>-0.5125</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0</v>
+        <v>0.4244806288601909</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0.7845</v>
+        <v>0.5125</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0.08333333333333333</v>
       </c>
     </row>
     <row r="87">
@@ -22018,40 +22021,40 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO FAMILIAR</t>
+          <t>LECHE SABOR BREAK INDIVIDUAL</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>30002078</v>
+        <v>30001407</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>LECHE PLATANO LONCOLECHE 12X1LT</t>
+          <t>LECHE BREAK CHOCO AVELLANA LONCO18X250ML</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.7174</v>
+        <v>0.8528</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>0.324</v>
+        <v>0.2475</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.3</v>
+        <v>0.1845</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0.024</v>
+        <v>0.063</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-0.3934</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.4516308893225536</v>
+        <v>0.2902204502814259</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0.3934</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="M87" s="3" t="n">
-        <v>0.07407407407407407</v>
+        <v>0.2545454545454546</v>
       </c>
     </row>
     <row r="88">
@@ -22071,36 +22074,36 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>30002066</v>
+        <v>30002065</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LECHE FRUTILLA LONCOLECHE 12X1LT</t>
+          <t>LECHE CHOCOLATE LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.6521</v>
+        <v>2.5934</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>0.168</v>
+        <v>0.732</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0.132</v>
+        <v>0.708</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>-0.4841</v>
+        <v>-1.8614</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.2576291979757706</v>
+        <v>0.2822549548854785</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0.4841</v>
+        <v>1.8614</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0.2142857142857142</v>
+        <v>0.01639344262295082</v>
       </c>
     </row>
     <row r="89">
@@ -22120,36 +22123,33 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>30002077</v>
+        <v>30002076</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LECHE VAINILLA LONCOLECHE 12X1LT</t>
+          <t>LECHE DESC LIGHT CHOC LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.3617</v>
+        <v>0.7845</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-0.2897</v>
+        <v>-0.7845</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.1990599944705557</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0.2897</v>
-      </c>
-      <c r="M89" s="3" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="90">
@@ -22165,40 +22165,40 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO INDIVIDUAL</t>
+          <t>LECHE SABOR LONCO FAMILIAR</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>30000400</v>
+        <v>30002078</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LECHE CHOC LONCO 30X200ML</t>
+          <t>LECHE PLATANO LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4.8718</v>
+        <v>0.7174</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.324</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0.636</v>
+        <v>0.3</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0.048</v>
+        <v>0.024</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>-4.1878</v>
+        <v>-0.3934</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.1403998522106819</v>
+        <v>0.4516308893225536</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>4.1878</v>
+        <v>0.3934</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>0.07017543859649122</v>
+        <v>0.07407407407407407</v>
       </c>
     </row>
     <row r="91">
@@ -22214,40 +22214,40 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO INDIVIDUAL</t>
+          <t>LECHE SABOR LONCO FAMILIAR</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>30000401</v>
+        <v>30002066</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>LECHE LONCO FRUTILLA 30X200ML</t>
+          <t>LECHE FRUTILLA LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>2.035</v>
+        <v>0.6521</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0.006</v>
+        <v>0.036</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-1.219</v>
+        <v>-0.4841</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.4009828009828009</v>
+        <v>0.2576291979757706</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1.219</v>
+        <v>0.4841</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0.007352941176470589</v>
+        <v>0.2142857142857142</v>
       </c>
     </row>
     <row r="92">
@@ -22263,40 +22263,40 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LECHE SABOR LONCO INDIVIDUAL</t>
+          <t>LECHE SABOR LONCO FAMILIAR</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>30000300</v>
+        <v>30002077</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LECHE PLATANO LONCO 30X200ML</t>
+          <t>LECHE VAINILLA LONCOLECHE 12X1LT</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>1.8669</v>
+        <v>0.3617</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>0.456</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.372</v>
+        <v>0.024</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-1.4109</v>
+        <v>-0.2897</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.2442551823879158</v>
+        <v>0.1990599944705557</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1.4109</v>
+        <v>0.2897</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="93">
@@ -22316,36 +22316,36 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>30000351</v>
+        <v>30000400</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LECHE VAINILLA 30X200ML</t>
+          <t>LECHE CHOC LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>1.2851</v>
+        <v>4.8718</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.3</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>0.3</v>
+        <v>0.636</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>-0.9850999999999999</v>
+        <v>-4.1878</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0.2334448681036495</v>
+        <v>0.1403998522106819</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0.9850999999999999</v>
+        <v>4.1878</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>0</v>
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="94">
@@ -22365,36 +22365,36 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>30000355</v>
+        <v>30000401</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>LECHE LONCO DESC CHOC 5X6X200ML</t>
+          <t>LECHE LONCO FRUTILLA 30X200ML</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.7917</v>
+        <v>2.035</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.042</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0.042</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>-0.7496999999999999</v>
+        <v>-1.219</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>0.05305039787798409</v>
+        <v>0.4009828009828009</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0.7496999999999999</v>
+        <v>1.219</v>
       </c>
       <c r="M94" s="3" t="n">
-        <v>0</v>
+        <v>0.007352941176470589</v>
       </c>
     </row>
     <row r="95">
@@ -22410,40 +22410,40 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
+          <t>LECHE SABOR LONCO INDIVIDUAL</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>30000328</v>
+        <v>30000300</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LECHE LONCO S/LACTOSA CHOCO 12X1LT</t>
+          <t>LECHE PLATANO LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.8072</v>
+        <v>1.8669</v>
       </c>
       <c r="G95" s="2" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="I95" s="2" t="n">
         <v>0.08400000000000001</v>
       </c>
-      <c r="H95" s="2" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>0.012</v>
-      </c>
       <c r="J95" s="2" t="n">
-        <v>-0.7232000000000001</v>
+        <v>-1.4109</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>0.1040634291377602</v>
+        <v>0.2442551823879158</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0.7232000000000001</v>
+        <v>1.4109</v>
       </c>
       <c r="M95" s="3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1842105263157895</v>
       </c>
     </row>
     <row r="96">
@@ -22459,37 +22459,37 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
+          <t>LECHE SABOR LONCO INDIVIDUAL</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>30000327</v>
+        <v>30000351</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LECHE LONCO S/LACTOSA FRUTILLA 12X1LT</t>
+          <t>LECHE VAINILLA 30X200ML</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.391</v>
+        <v>1.2851</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I96" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-0.319</v>
+        <v>-0.9850999999999999</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.1841432225063938</v>
+        <v>0.2334448681036495</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0.319</v>
+        <v>0.9850999999999999</v>
       </c>
       <c r="M96" s="3" t="n">
         <v>0</v>
@@ -22508,40 +22508,40 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
+          <t>LECHE SABOR LONCO INDIVIDUAL</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>30000421</v>
+        <v>30000355</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LECHE S/LACTOSA VAINILLA 12X1LT</t>
+          <t>LECHE LONCO DESC CHOC 5X6X200ML</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.2535</v>
+        <v>0.7917</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>-0.1695</v>
+        <v>-0.7496999999999999</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>0.3313609467455622</v>
+        <v>0.05305039787798409</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0.1695</v>
+        <v>0.7496999999999999</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -22557,40 +22557,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
+          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>30000398</v>
+        <v>30000328</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LECHE S/LACT CHOC LONCO 30X200ML</t>
+          <t>LECHE LONCO S/LACTOSA CHOCO 12X1LT</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>1.3636</v>
+        <v>0.8072</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.588</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>0.138</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0.45</v>
+        <v>0.012</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>-0.7756</v>
+        <v>-0.7232000000000001</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>0.431211498973306</v>
+        <v>0.1040634291377602</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0.7756</v>
+        <v>0.7232000000000001</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>0.7653061224489797</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="99">
@@ -22606,40 +22606,40 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
+          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>30000354</v>
+        <v>30000327</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LECHE LONCO SEMI S/LACTOSA 5X6X200ML</t>
+          <t>LECHE LONCO S/LACTOSA FRUTILLA 12X1LT</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.5445</v>
+        <v>0.391</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>0.336</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>0.33</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>-0.2085</v>
+        <v>-0.319</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.6170798898071626</v>
+        <v>0.1841432225063938</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0.2085</v>
+        <v>0.319</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -22655,40 +22655,40 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LONCO BASE</t>
+          <t>LECHE SABOR SIN LACTOSA FAMILIAR</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>30000522</v>
+        <v>30000421</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LECHE BLANCA LONCO ENTERA BASE 12X1LT</t>
+          <t>LECHE S/LACTOSA VAINILLA 12X1LT</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>80</v>
+        <v>0.2535</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>18.612</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>18.576</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>-61.38800000000001</v>
+        <v>-0.1695</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0.23265</v>
+        <v>0.3313609467455622</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>61.38800000000001</v>
+        <v>0.1695</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0.001934235976789168</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="101">
@@ -22704,40 +22704,40 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LONCO BASE</t>
+          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>30000524</v>
+        <v>30000398</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LECHE BLANCA LONCO DESC BASE 12X1LT</t>
+          <t>LECHE S/LACT CHOC LONCO 30X200ML</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>8.275399999999999</v>
+        <v>1.3636</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.624</v>
+        <v>0.588</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>0.552</v>
+        <v>0.138</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>-7.6514</v>
+        <v>-0.7756</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.0754042100683955</v>
+        <v>0.431211498973306</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>7.6514</v>
+        <v>0.7756</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.7653061224489797</v>
       </c>
     </row>
     <row r="102">
@@ -22753,40 +22753,40 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LONCO BASE</t>
+          <t>LECHE SABOR SIN LACTOSA INDIVIDUAL</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>30000523</v>
+        <v>30000354</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LECHE BLANCA LONCO SEMI BASE 12X1LT</t>
+          <t>LECHE LONCO SEMI S/LACTOSA 5X6X200ML</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>5.5</v>
+        <v>0.5445</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>4.608</v>
+        <v>0.336</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>4.584</v>
+        <v>0.33</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0.024</v>
+        <v>0.006</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>-0.8920000000000003</v>
+        <v>-0.2085</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0.8378181818181818</v>
+        <v>0.6170798898071626</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0.8920000000000003</v>
+        <v>0.2085</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>0.005208333333333334</v>
+        <v>0.01785714285714286</v>
       </c>
     </row>
     <row r="103">
@@ -22802,40 +22802,40 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LONCO BASE 200</t>
+          <t>LONCO BASE</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>30002285</v>
+        <v>30000522</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LECHE LONCO ENTERA 5X6X200ML</t>
+          <t>LECHE BLANCA LONCO ENTERA BASE 12X1LT</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.471</v>
+        <v>80</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>0.108</v>
+        <v>18.612</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>0.108</v>
+        <v>18.576</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-0.363</v>
+        <v>-61.38800000000001</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0.2292993630573248</v>
+        <v>0.23265</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0.363</v>
+        <v>61.38800000000001</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.001934235976789168</v>
       </c>
     </row>
     <row r="104">
@@ -22851,40 +22851,40 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LONCO BASE 200</t>
+          <t>LONCO BASE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>30002282</v>
+        <v>30000524</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LECHE LONCO SEMI DESCR 5X6X200ML</t>
+          <t>LECHE BLANCA LONCO DESC BASE 12X1LT</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.2333</v>
+        <v>8.275399999999999</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>0.024</v>
+        <v>0.624</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>0.024</v>
+        <v>0.552</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>-0.2093</v>
+        <v>-7.6514</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>0.1028718388341192</v>
+        <v>0.0754042100683955</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0.2093</v>
+        <v>7.6514</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>0</v>
+        <v>0.1153846153846154</v>
       </c>
     </row>
     <row r="105">
@@ -22900,40 +22900,40 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MANJAR</t>
+          <t>LONCO BASE</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>30002284</v>
+        <v>30000523</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MANJAR EN BARRA 120X35GR</t>
+          <t>LECHE BLANCA LONCO SEMI BASE 12X1LT</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.1283</v>
+        <v>5.5</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.0294</v>
+        <v>4.608</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>0.0294</v>
+        <v>4.584</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>-0.0989</v>
+        <v>-0.8920000000000003</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>0.2291504286827747</v>
+        <v>0.8378181818181818</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0.0989</v>
+        <v>0.8920000000000003</v>
       </c>
       <c r="M105" s="3" t="n">
-        <v>0</v>
+        <v>0.005208333333333334</v>
       </c>
     </row>
     <row r="106">
@@ -22949,40 +22949,40 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MANJAR DOYPACK</t>
+          <t>LONCO BASE 200</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>30002098</v>
+        <v>30002285</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MANJAR LONCOLECHE DP 12X750GR</t>
+          <t>LECHE LONCO ENTERA 5X6X200ML</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>1.131</v>
+        <v>0.471</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>0.126</v>
+        <v>0.108</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>0.108</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>-1.005</v>
+        <v>-0.363</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.1114058355437666</v>
+        <v>0.2292993630573248</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1.005</v>
+        <v>0.363</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -22998,40 +22998,40 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MANJAR RETAIL</t>
+          <t>LONCO BASE 200</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>30002177</v>
+        <v>30002282</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MANJAR LONCOLECHE BOLSA 10X920GR</t>
+          <t>LECHE LONCO SEMI DESCR 5X6X200ML</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>4.8028</v>
+        <v>0.2333</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>0.7728</v>
+        <v>0.024</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>0.6072</v>
+        <v>0.024</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0.1656</v>
+        <v>0</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>-4.03</v>
+        <v>-0.2093</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.1609061380861164</v>
+        <v>0.1028718388341192</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>4.03</v>
+        <v>0.2093</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0.2142857142857143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -23047,40 +23047,40 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MOMENTS FAMILIAR</t>
+          <t>MANJAR</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>30000010</v>
+        <v>30002284</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>LECHE MOMENTS CAPUCHINO 12X1LT</t>
+          <t>MANJAR EN BARRA 120X35GR</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.9597</v>
+        <v>0.1283</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0294</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>0.024</v>
+        <v>0.0294</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>-0.9117</v>
+        <v>-0.0989</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0.05001562988433886</v>
+        <v>0.2291504286827747</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0.9117</v>
+        <v>0.0989</v>
       </c>
       <c r="M108" s="3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -23096,40 +23096,40 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MOMENTS FAMILIAR</t>
+          <t>MANJAR DOYPACK</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>30000006</v>
+        <v>30002098</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LECHE UHT MOMENTS MOCA 12X1LT</t>
+          <t>MANJAR LONCOLECHE DP 12X750GR</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>0.6254999999999999</v>
+        <v>1.131</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.048</v>
+        <v>0.126</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>0.024</v>
+        <v>0.108</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>-0.5774999999999999</v>
+        <v>-1.005</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>0.07673860911270984</v>
+        <v>0.1114058355437666</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>0.5774999999999999</v>
+        <v>1.005</v>
       </c>
       <c r="M109" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="110">
@@ -23145,40 +23145,40 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MOMENTS INDIVIDUAL</t>
+          <t>MANJAR RETAIL</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>30002359</v>
+        <v>30002177</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LECHE BON MOMENT DAN CAPPUCCINO 5X6X200ML</t>
+          <t>MANJAR LONCOLECHE BOLSA 10X920GR</t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>1.1909</v>
+        <v>4.8028</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.33</v>
+        <v>0.7728</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>0.06</v>
+        <v>0.6072</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0.27</v>
+        <v>0.1656</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>-0.8609</v>
+        <v>-4.03</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0.2771013519187169</v>
+        <v>0.1609061380861164</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0.8609</v>
+        <v>4.03</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.2142857142857143</v>
       </c>
     </row>
     <row r="111">
@@ -23194,40 +23194,40 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MOMENTS INDIVIDUAL</t>
+          <t>MOMENTS FAMILIAR</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>30002358</v>
+        <v>30000010</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>LECHE BON MOMENT DAN MOCACCINO 5X6X200ML</t>
+          <t>LECHE MOMENTS CAPUCHINO 12X1LT</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.9597</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.168</v>
+        <v>0.048</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>0.078</v>
+        <v>0.024</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0.09</v>
+        <v>0.024</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>-0.8101999999999999</v>
+        <v>-0.9117</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0.171744019627888</v>
+        <v>0.05001562988433886</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0.8101999999999999</v>
+        <v>0.9117</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="112">
@@ -23243,37 +23243,40 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MOMENTS INDIVIDUAL</t>
+          <t>MOMENTS FAMILIAR</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>30001414</v>
+        <v>30000006</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>BON MOMENT CAPPUCCINO 18X200ML</t>
+          <t>LECHE UHT MOMENTS MOCA 12X1LT</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>0.0036</v>
+        <v>0.048</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0036</v>
+        <v>-0.5774999999999999</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0.07673860911270984</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>0</v>
+        <v>0.5774999999999999</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="113">
@@ -23293,33 +23296,36 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>30001415</v>
+        <v>30002359</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>BON MOMENT MOCACCINO 18X200ML</t>
+          <t>LECHE BON MOMENT DAN CAPPUCCINO 5X6X200ML</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0</v>
+        <v>1.1909</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.0036</v>
+        <v>0.33</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0036</v>
+        <v>-0.8609</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>0.2771013519187169</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>0.8609</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>0</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="114">
@@ -23335,37 +23341,40 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NECTAR 115</t>
+          <t>MOMENTS INDIVIDUAL</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>30002229</v>
+        <v>30002358</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NECTAR WATT'S DURAZNO 10X5X115ML</t>
+          <t>LECHE BON MOMENT DAN MOCACCINO 5X6X200ML</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0.0575</v>
+        <v>0.9782</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0</v>
+        <v>0.168</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>0</v>
+        <v>0.078</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>-0.0575</v>
+        <v>-0.8101999999999999</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>0.171744019627888</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0.0575</v>
+        <v>0.8101999999999999</v>
+      </c>
+      <c r="M114" s="3" t="n">
+        <v>0.5357142857142857</v>
       </c>
     </row>
     <row r="115">
@@ -23381,22 +23390,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NECTAR 115</t>
+          <t>MOMENTS INDIVIDUAL</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>30002230</v>
+        <v>30001414</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>NECTAR WATTS MANZANA 5X10X115ML</t>
+          <t>BON MOMENT CAPPUCCINO 18X200ML</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0.0575</v>
+        <v>0</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>0</v>
@@ -23405,13 +23414,13 @@
         <v>0</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>-0.0575</v>
-      </c>
-      <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.0036</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0.0575</v>
+        <v>0</v>
+      </c>
+      <c r="M115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -23427,40 +23436,37 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NECTAR 115 PROBIOTICOS</t>
+          <t>MOMENTS INDIVIDUAL</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>30002261</v>
+        <v>30001415</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PROBIOTICO DURAZNO 5X6X115ML</t>
+          <t>BON MOMENT MOCACCINO 18X200ML</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.1949</v>
+        <v>0</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>0.0104</v>
+        <v>0.0036</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0.0034</v>
+        <v>0</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>-0.1845</v>
-      </c>
-      <c r="K116" s="3" t="n">
-        <v>0.05336069779374038</v>
+        <v>0.0036</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>0.1845</v>
+        <v>0</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0.3269230769230769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -23476,40 +23482,37 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NECTAR 115 PROBIOTICOS</t>
+          <t>NECTAR 115</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>30002262</v>
+        <v>30002229</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PROBIOTICO MANZANA 5X6X115ML</t>
+          <t>NECTAR WATT'S DURAZNO 10X5X115ML</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.1551</v>
+        <v>0.0575</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.0173</v>
+        <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>0.0069</v>
+        <v>0</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>-0.1378</v>
+        <v>-0.0575</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>0.1115409413281754</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>0.1378</v>
-      </c>
-      <c r="M117" s="3" t="n">
-        <v>0.6011560693641619</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="118">
@@ -23525,40 +23528,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NECTAR INDIVIDUAL 0%</t>
+          <t>NECTAR 115</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>30001684</v>
+        <v>30002230</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NECTAR WATTS DZNO S/A 30X200ML</t>
+          <t>NECTAR WATTS MANZANA 5X10X115ML</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>1.9752</v>
+        <v>0.0575</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.246</v>
+        <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>-1.7292</v>
+        <v>-0.0575</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.1245443499392467</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1.7292</v>
-      </c>
-      <c r="M118" s="3" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="119">
@@ -23574,40 +23574,40 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
+          <t>NECTAR 115 PROBIOTICOS</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>30000254</v>
+        <v>30002261</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>NECTAR WATTS NJA LIGHT SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS PROBIOTICO DURAZNO 5X6X115ML</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>3.2068</v>
+        <v>0.1949</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1.092</v>
+        <v>0.0104</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>1.014</v>
+        <v>0.0069</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0034</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>-2.1148</v>
+        <v>-0.1845</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>0.3405263814394413</v>
+        <v>0.05336069779374038</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>2.1148</v>
+        <v>0.1845</v>
       </c>
       <c r="M119" s="3" t="n">
-        <v>0.03846153846153846</v>
+        <v>0.3269230769230769</v>
       </c>
     </row>
     <row r="120">
@@ -23623,40 +23623,40 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
+          <t>NECTAR 115 PROBIOTICOS</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>30000206</v>
+        <v>30002262</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>NECTAR WATTS MZNA LIGHT 30X200ML</t>
+          <t>NECTAR WATTS PROBIOTICO MANZANA 5X6X115ML</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>2.1162</v>
+        <v>0.1551</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>0.126</v>
+        <v>0.0173</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0069</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0104</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>-1.9902</v>
+        <v>-0.1378</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0.05954068613552594</v>
+        <v>0.1115409413281754</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1.9902</v>
+        <v>0.1378</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.6011560693641619</v>
       </c>
     </row>
     <row r="121">
@@ -23672,40 +23672,40 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
+          <t>NECTAR INDIVIDUAL 0%</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>30000207</v>
+        <v>30001684</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PIÑA LIGHT 30X200ML</t>
+          <t>NECTAR WATTS DZNO S/A 30X200ML</t>
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>1.7032</v>
+        <v>1.9752</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.3</v>
+        <v>0.246</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>0.192</v>
+        <v>0.144</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0.09</v>
+        <v>0.078</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>-1.4032</v>
+        <v>-1.7292</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0.176139032409582</v>
+        <v>0.1245443499392467</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1.4032</v>
+        <v>1.7292</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0.3</v>
+        <v>0.3170731707317073</v>
       </c>
     </row>
     <row r="122">
@@ -23721,40 +23721,40 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR FAMILIAR</t>
+          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>30000244</v>
+        <v>30000254</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>NECTAR WATTS NARANJA 12X1LT</t>
+          <t>NECTAR WATTS NJA LIGHT SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>3.3473</v>
+        <v>3.2068</v>
       </c>
       <c r="G122" s="2" t="n">
         <v>1.092</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>1.008</v>
+        <v>1.014</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-2.2553</v>
+        <v>-2.1148</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0.3262330833806352</v>
+        <v>0.3405263814394413</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>2.2553</v>
+        <v>2.1148</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.03846153846153846</v>
       </c>
     </row>
     <row r="123">
@@ -23770,40 +23770,40 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR FAMILIAR</t>
+          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>30000246</v>
+        <v>30000206</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>NECTAR WATTS DURAZNO 12X1LT</t>
+          <t>NECTAR WATTS MZNA LIGHT 30X200ML</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>2.8323</v>
+        <v>2.1162</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>0.852</v>
+        <v>0.126</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>0.72</v>
+        <v>0.048</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>0.132</v>
+        <v>0.048</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-1.9803</v>
+        <v>-1.9902</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0.3008155915686898</v>
+        <v>0.05954068613552594</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1.9803</v>
+        <v>1.9902</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>0.1549295774647887</v>
+        <v>0.3809523809523809</v>
       </c>
     </row>
     <row r="124">
@@ -23819,40 +23819,40 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR FAMILIAR</t>
+          <t>NECTAR WATTS LIGHT INDIVIDUAL</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>30000245</v>
+        <v>30000207</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>NECTAR WATTS MANZANA 12X1LT</t>
+          <t>NECTAR WATTS PIÑA LIGHT 30X200ML</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>2.6489</v>
+        <v>1.7032</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>0.288</v>
+        <v>0.192</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0.132</v>
+        <v>0.09</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>-2.2289</v>
+        <v>-1.4032</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0.1585563818943713</v>
+        <v>0.176139032409582</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>2.2289</v>
+        <v>1.4032</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="125">
@@ -23872,36 +23872,36 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>30000248</v>
+        <v>30000244</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PIÑA 12X1LT</t>
+          <t>NECTAR WATTS NARANJA 12X1LT</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>2.578</v>
+        <v>3.3473</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.984</v>
+        <v>1.092</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>0.864</v>
+        <v>1.008</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>0.12</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>-1.594</v>
+        <v>-2.2553</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0.3816912335143522</v>
+        <v>0.3262330833806352</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1.594</v>
+        <v>2.2553</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="126">
@@ -23917,40 +23917,40 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>NECTAR WATTS REGULAR FAMILIAR</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>30000255</v>
+        <v>30000246</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>NECTAR WATTS DZNO SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS DURAZNO 12X1LT</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>10.1369</v>
+        <v>2.8323</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1.62</v>
+        <v>0.852</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>0.948</v>
+        <v>0.72</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>0.648</v>
+        <v>0.132</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>-8.5169</v>
+        <v>-1.9803</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0.1598121713738914</v>
+        <v>0.3008155915686898</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>8.5169</v>
+        <v>1.9803</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1549295774647887</v>
       </c>
     </row>
     <row r="127">
@@ -23966,40 +23966,40 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>NECTAR WATTS REGULAR FAMILIAR</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>30000256</v>
+        <v>30000245</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PIÑA SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS MANZANA 12X1LT</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>7.8254</v>
+        <v>2.6489</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>1.398</v>
+        <v>0.42</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>1.074</v>
+        <v>0.288</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>0.3</v>
+        <v>0.132</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>-6.4274</v>
+        <v>-2.2289</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>0.17864901474685</v>
+        <v>0.1585563818943713</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>6.4274</v>
+        <v>2.2289</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>0.2145922746781116</v>
+        <v>0.3142857142857143</v>
       </c>
     </row>
     <row r="128">
@@ -24015,40 +24015,40 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>NECTAR WATTS REGULAR FAMILIAR</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>30000257</v>
+        <v>30000248</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NECTAR WATTS MZNA SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS PIÑA 12X1LT</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>7.0865</v>
+        <v>2.578</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2.238</v>
+        <v>0.984</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>1.698</v>
+        <v>0.864</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0.516</v>
+        <v>0.12</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>-4.8485</v>
+        <v>-1.594</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>0.3158117547449376</v>
+        <v>0.3816912335143522</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>4.8485</v>
+        <v>1.594</v>
       </c>
       <c r="M128" s="3" t="n">
-        <v>0.2305630026809652</v>
+        <v>0.1219512195121951</v>
       </c>
     </row>
     <row r="129">
@@ -24068,36 +24068,36 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>30000258</v>
+        <v>30000255</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>NECTAR WATTS NJA SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS DZNO SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>7.0123</v>
+        <v>10.1369</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>2.178</v>
+        <v>1.62</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>1.668</v>
+        <v>0.948</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>0.486</v>
+        <v>0.648</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>-4.8343</v>
+        <v>-8.5169</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>0.3105970936782511</v>
+        <v>0.1598121713738914</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>4.8343</v>
+        <v>8.5169</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>0.2231404958677686</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="130">
@@ -24117,36 +24117,36 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>30002099</v>
+        <v>30000256</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NECTAR WATTS TUTTIFLLA SIXPACK 30X200ML</t>
+          <t>NECTAR WATTS PIÑA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>3.4215</v>
+        <v>7.8254</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.606</v>
+        <v>1.398</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>0.45</v>
+        <v>1.074</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0.132</v>
+        <v>0.3</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>-2.8155</v>
+        <v>-6.4274</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>0.1771153003068829</v>
+        <v>0.17864901474685</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2.8155</v>
+        <v>6.4274</v>
       </c>
       <c r="M130" s="3" t="n">
-        <v>0.2178217821782178</v>
+        <v>0.2145922746781116</v>
       </c>
     </row>
     <row r="131">
@@ -24162,40 +24162,40 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR PROTEINA</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>30002291</v>
+        <v>30000257</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PROTEINA TROPICAL SIXPACK 18X250ML</t>
+          <t>NECTAR WATTS MZNA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0.3898</v>
+        <v>7.0865</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>0.0675</v>
+        <v>2.238</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>0.0675</v>
+        <v>1.698</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>-0.3223</v>
+        <v>-4.8485</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>0.1731657260133402</v>
+        <v>0.3158117547449376</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>0.3223</v>
+        <v>4.8485</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>0</v>
+        <v>0.2305630026809652</v>
       </c>
     </row>
     <row r="132">
@@ -24211,40 +24211,40 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR PROTEINA</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>30002325</v>
+        <v>30000258</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NECTAR WATTS PROTEINA FRUTOS ROJOS SIXPACK 18X250ML</t>
+          <t>NECTAR WATTS NJA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.21</v>
+        <v>7.0123</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>2.178</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>1.668</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>-0.201</v>
+        <v>-4.8343</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0.04285714285714286</v>
+        <v>0.3105970936782511</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0.201</v>
+        <v>4.8343</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>0</v>
+        <v>0.2231404958677686</v>
       </c>
     </row>
     <row r="133">
@@ -24260,40 +24260,40 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PROTEIN MILK BLANCA FAMILIAR</t>
+          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>30000481</v>
+        <v>30002099</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>LECHE LONCO EXTRA PROTEINA 12X1LT</t>
+          <t>NECTAR WATTS TUTTIFLLA SIXPACK 30X200ML</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>3.5804</v>
+        <v>3.4215</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>0.504</v>
+        <v>0.606</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0.144</v>
+        <v>0.132</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>-3.0764</v>
+        <v>-2.8155</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>0.1407663948162217</v>
+        <v>0.1771153003068829</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>3.0764</v>
+        <v>2.8155</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2178217821782178</v>
       </c>
     </row>
     <row r="134">
@@ -24309,40 +24309,40 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA FAMILIAR</t>
+          <t>NECTAR WATTS REGULAR PROTEINA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>30000516</v>
+        <v>30002291</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN MILK CHOCO 12X1LT</t>
+          <t>NECTAR WATTS PROTEINA TROPICAL SIXPACK 18X250ML</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>2.5189</v>
+        <v>0.3898</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>0.624</v>
+        <v>0.0675</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>0.468</v>
+        <v>0.0675</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>-1.8949</v>
+        <v>-0.3223</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0.2477271825002978</v>
+        <v>0.1731657260133402</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1.8949</v>
+        <v>0.3223</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -24358,40 +24358,40 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA FAMILIAR</t>
+          <t>NECTAR WATTS REGULAR PROTEINA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>30000514</v>
+        <v>30002325</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN MILK CAPP 12X1LT</t>
+          <t>NECTAR WATTS PROTEINA FRUTOS ROJOS SIXPACK 18X250ML</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>2.2472</v>
+        <v>0.21</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>1.152</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>1.08</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>-1.0952</v>
+        <v>-0.201</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>0.5126379494482022</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>1.0952</v>
+        <v>0.201</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -24407,40 +24407,40 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
+          <t>PROTEIN MILK BLANCA FAMILIAR</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>30002330</v>
+        <v>30000481</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN CHOCOLATE 30X200ML</t>
+          <t>LECHE LONCO EXTRA PROTEINA 12X1LT</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>3.1363</v>
+        <v>3.5804</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2.22</v>
+        <v>0.504</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>2.01</v>
+        <v>0.36</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0.21</v>
+        <v>0.144</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>-0.9162999999999997</v>
+        <v>-3.0764</v>
       </c>
       <c r="K136" s="3" t="n">
-        <v>0.7078404489366452</v>
+        <v>0.1407663948162217</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0.9162999999999997</v>
+        <v>3.0764</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>0.09459459459459459</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="137">
@@ -24456,40 +24456,40 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
+          <t>PROTEIN MILK SABORADA FAMILIAR</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>30002329</v>
+        <v>30000516</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN CAPPUCCINO 30X200ML</t>
+          <t>LECHE LONCO PROTEIN MILK CHOCO 12X1LT</t>
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>2.7665</v>
+        <v>2.5189</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.732</v>
+        <v>0.624</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>0.678</v>
+        <v>0.468</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0.054</v>
+        <v>0.156</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>-2.0345</v>
+        <v>-1.8949</v>
       </c>
       <c r="K137" s="3" t="n">
-        <v>0.2645942526658232</v>
+        <v>0.2477271825002978</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2.0345</v>
+        <v>1.8949</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>0.07377049180327869</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="138">
@@ -24505,40 +24505,40 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
+          <t>PROTEIN MILK SABORADA FAMILIAR</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>30001423</v>
+        <v>30000514</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>LECHE FULL LONCO PROTEIN VLLA 18X250ML</t>
+          <t>LECHE LONCO PROTEIN MILK CAPP 12X1LT</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>2.0042</v>
+        <v>2.2472</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.5715</v>
+        <v>1.152</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>0.297</v>
+        <v>1.08</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0.2745</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>-1.4327</v>
+        <v>-1.0952</v>
       </c>
       <c r="K138" s="3" t="n">
-        <v>0.2851511825167149</v>
+        <v>0.5126379494482022</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1.4327</v>
+        <v>1.0952</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>0.4803149606299213</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="139">
@@ -24558,36 +24558,36 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>30001411</v>
+        <v>30002330</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN CAPPUCCINO 18X200ML</t>
+          <t>LECHE LONCO PROTEIN CHOCOLATE 30X200ML</t>
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>1.6317</v>
+        <v>3.1363</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>0.0036</v>
+        <v>2.22</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0.0036</v>
+        <v>0.21</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>-1.6281</v>
+        <v>-0.9162999999999997</v>
       </c>
       <c r="K139" s="3" t="n">
-        <v>0.002206287920573635</v>
+        <v>0.7078404489366452</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1.6281</v>
+        <v>0.9162999999999997</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>1</v>
+        <v>0.09459459459459459</v>
       </c>
     </row>
     <row r="140">
@@ -24607,36 +24607,36 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>30001376</v>
+        <v>30002329</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>LECHE LONCO FULL PROTEIN CHOCOLATE18X250</t>
+          <t>LECHE LONCO PROTEIN CAPPUCCINO 30X200ML</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>1.2315</v>
+        <v>2.7665</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.3195</v>
+        <v>0.732</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>0.1755</v>
+        <v>0.678</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>0.144</v>
+        <v>0.054</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>-0.912</v>
+        <v>-2.0345</v>
       </c>
       <c r="K140" s="3" t="n">
-        <v>0.2594397076735688</v>
+        <v>0.2645942526658232</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0.912</v>
+        <v>2.0345</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>0.4507042253521126</v>
+        <v>0.07377049180327869</v>
       </c>
     </row>
     <row r="141">
@@ -24656,36 +24656,36 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>30001980</v>
+        <v>30001423</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>LECHE FULL PRO CAPPUCCINO LONCO 18X250ML</t>
+          <t>LECHE FULL LONCO PROTEIN VLLA 18X250ML</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>0.5009</v>
+        <v>2.0042</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5715</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>0.4725</v>
+        <v>0.297</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0.2115</v>
+        <v>0.2745</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.1831</v>
+        <v>-1.4327</v>
       </c>
       <c r="K141" s="3" t="n">
-        <v>1.365542024356159</v>
+        <v>0.2851511825167149</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>1.4327</v>
       </c>
       <c r="M141" s="3" t="n">
-        <v>0.3092105263157894</v>
+        <v>0.4803149606299213</v>
       </c>
     </row>
     <row r="142">
@@ -24705,36 +24705,36 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>30002272</v>
+        <v>30001411</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LECHE LONCO EXTRAPROTEIN 18X200ML</t>
+          <t>LECHE LONCO PROTEIN CAPPUCCINO 18X200ML</t>
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0.2917</v>
+        <v>1.6317</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.048</v>
+        <v>0.0036</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>0.042</v>
+        <v>0.0036</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>-0.2437</v>
+        <v>-1.6281</v>
       </c>
       <c r="K142" s="3" t="n">
-        <v>0.164552622557422</v>
+        <v>0.002206287920573635</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0.2437</v>
+        <v>1.6281</v>
       </c>
       <c r="M142" s="3" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -24754,36 +24754,36 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>30001412</v>
+        <v>30001376</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LECHE LONCO PROTEIN CHOCOLATE 18X200ML</t>
+          <t>LECHE LONCO FULL PROTEIN CHOCOLATE18X250</t>
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0.0602</v>
+        <v>1.2315</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.0108</v>
+        <v>0.3195</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>0</v>
+        <v>0.1755</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>-0.0494</v>
+        <v>-0.912</v>
       </c>
       <c r="K143" s="3" t="n">
-        <v>0.1794019933554817</v>
+        <v>0.2594397076735688</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>0.0494</v>
+        <v>0.912</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>0</v>
+        <v>0.4507042253521126</v>
       </c>
     </row>
     <row r="144">
@@ -24799,40 +24799,40 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SHAKE SHAKE INDIVIDUAL</t>
+          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>30002180</v>
+        <v>30001980</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SHAKE SHAKE MANJAR 30X190ML</t>
+          <t>LECHE FULL PRO CAPPUCCINO LONCO 18X250ML</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1.7242</v>
+        <v>0.5009</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>0.228</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>0.2052</v>
+        <v>0.4725</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.2115</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>-1.4962</v>
+        <v>0.1831</v>
       </c>
       <c r="K144" s="3" t="n">
-        <v>0.1322352395313769</v>
+        <v>1.365542024356159</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1.4962</v>
+        <v>0</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>0.1</v>
+        <v>0.3092105263157894</v>
       </c>
     </row>
     <row r="145">
@@ -24848,40 +24848,40 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SHAKE SHAKE INDIVIDUAL</t>
+          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>30002178</v>
+        <v>30002272</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>SHAKE SHAKE CHOCOLATE 30X190ML</t>
+          <t>LECHE LONCO EXTRAPROTEIN 18X200ML</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0.6909</v>
+        <v>0.2917</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.1539</v>
+        <v>0.048</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>0.1368</v>
+        <v>0.006</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.042</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>-0.5369999999999999</v>
+        <v>-0.2437</v>
       </c>
       <c r="K145" s="3" t="n">
-        <v>0.2227529309596179</v>
+        <v>0.164552622557422</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>0.5369999999999999</v>
+        <v>0.2437</v>
       </c>
       <c r="M145" s="3" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="146">
@@ -24897,40 +24897,40 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>YOGU YOGU FAMILIAR</t>
+          <t>PROTEIN MILK SABORADA INDIVIDUAL</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>30001574</v>
+        <v>30001412</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>YOGU YOGU ORIGINAL MORA LV 12x1LT</t>
+          <t>LECHE LONCO PROTEIN CHOCOLATE 18X200ML</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>1.179</v>
+        <v>0.0602</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>0.252</v>
+        <v>0.0108</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>0.204</v>
+        <v>0</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-0.927</v>
+        <v>-0.0494</v>
       </c>
       <c r="K146" s="3" t="n">
-        <v>0.2137404580152672</v>
+        <v>0.1794019933554817</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>0.927</v>
+        <v>0.0494</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>0.1904761904761905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -24946,40 +24946,40 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YOGU YOGU INDIVIDUAL</t>
+          <t>SHAKE SHAKE INDIVIDUAL</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>30000309</v>
+        <v>30002180</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>YOGU YOGU MORA 30X200GR</t>
+          <t>SHAKE SHAKE MANJAR 30X190ML</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>14.6334</v>
+        <v>1.7242</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>4.956</v>
+        <v>0.228</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>4.794</v>
+        <v>0.2052</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>0.156</v>
+        <v>0.0228</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-9.677399999999999</v>
+        <v>-1.4962</v>
       </c>
       <c r="K147" s="3" t="n">
-        <v>0.3386772725408996</v>
+        <v>0.1322352395313769</v>
       </c>
       <c r="L147" s="2" t="n">
-        <v>9.677399999999999</v>
+        <v>1.4962</v>
       </c>
       <c r="M147" s="3" t="n">
-        <v>0.03147699757869249</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="148">
@@ -24995,40 +24995,40 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>YOGU YOGU INDIVIDUAL</t>
+          <t>SHAKE SHAKE INDIVIDUAL</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>30000305</v>
+        <v>30002178</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>YOGU YOGU FRUTILLA 30X200GR</t>
+          <t>SHAKE SHAKE CHOCOLATE 30X190ML</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>7.543</v>
+        <v>0.6909</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1.758</v>
+        <v>0.1539</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>1.68</v>
+        <v>0.1368</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>0.078</v>
+        <v>0.0171</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>-5.785</v>
+        <v>-0.5369999999999999</v>
       </c>
       <c r="K148" s="3" t="n">
-        <v>0.2330637677316718</v>
+        <v>0.2227529309596179</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>5.785</v>
+        <v>0.5369999999999999</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>0.04436860068259386</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="149">
@@ -25044,40 +25044,40 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>YOGU YOGU INDIVIDUAL</t>
+          <t>YOGU YOGU FAMILIAR</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>30000307</v>
+        <v>30001574</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>YOGU YOGU PINA 30X200GR</t>
+          <t>YOGU YOGU ORIGINAL MORA LV 12x1LT</t>
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>3.1042</v>
+        <v>1.179</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>0.912</v>
+        <v>0.252</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>0.9</v>
+        <v>0.204</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0.012</v>
+        <v>0.048</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>-2.1922</v>
+        <v>-0.927</v>
       </c>
       <c r="K149" s="3" t="n">
-        <v>0.2937955028670833</v>
+        <v>0.2137404580152672</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>2.1922</v>
+        <v>0.927</v>
       </c>
       <c r="M149" s="3" t="n">
-        <v>0.0131578947368421</v>
+        <v>0.1904761904761905</v>
       </c>
     </row>
     <row r="150">
@@ -25097,36 +25097,36 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>30000318</v>
+        <v>30000309</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>YOGU YOGU CHIRIMOYA 30X200GR</t>
+          <t>YOGU YOGU MORA 30X200GR</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>2.765</v>
+        <v>14.6334</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>1.968</v>
+        <v>4.956</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>1.95</v>
+        <v>4.794</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>0.018</v>
+        <v>0.156</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>-0.7970000000000002</v>
+        <v>-9.677399999999999</v>
       </c>
       <c r="K150" s="3" t="n">
-        <v>0.711754068716094</v>
+        <v>0.3386772725408996</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0.7970000000000002</v>
+        <v>9.677399999999999</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>0.009146341463414634</v>
+        <v>0.03147699757869249</v>
       </c>
     </row>
     <row r="151">
@@ -25146,36 +25146,36 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>30000306</v>
+        <v>30000305</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>YOGU YOGU DAMASCO 30X200GR</t>
+          <t>YOGU YOGU FRUTILLA 30X200GR</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>2.2004</v>
+        <v>7.543</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>1.776</v>
+        <v>1.758</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>1.728</v>
+        <v>1.68</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0.048</v>
+        <v>0.078</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>-0.4244000000000001</v>
+        <v>-5.785</v>
       </c>
       <c r="K151" s="3" t="n">
-        <v>0.8071259770950736</v>
+        <v>0.2330637677316718</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>0.4244000000000001</v>
+        <v>5.785</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.04436860068259386</v>
       </c>
     </row>
     <row r="152">
@@ -25195,42 +25195,42 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>30000308</v>
+        <v>30000307</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>YOGU YOGU VAINILLA 30X200GR</t>
+          <t>YOGU YOGU PINA 30X200GR</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>1.8164</v>
+        <v>3.1042</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>0.876</v>
+        <v>0.912</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>0.858</v>
+        <v>0.9</v>
       </c>
       <c r="I152" s="2" t="n">
         <v>0.012</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>-0.9404</v>
+        <v>-2.1922</v>
       </c>
       <c r="K152" s="3" t="n">
-        <v>0.4822726271746312</v>
+        <v>0.2937955028670833</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0.9404</v>
+        <v>2.1922</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.0131578947368421</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>Canal Tradicional</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -25240,46 +25240,46 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>YOGU YOGU INDIVIDUAL</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>30000258</v>
+        <v>30000318</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>NECTAR WATTS NJA SIXPACK 30X200ML</t>
+          <t>YOGU YOGU CHIRIMOYA 30X200GR</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>93</v>
+        <v>2.765</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>93.312</v>
+        <v>1.968</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>93.312</v>
+        <v>1.95</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.3119999999999976</v>
+        <v>-0.7970000000000002</v>
       </c>
       <c r="K153" s="3" t="n">
-        <v>1.003354838709677</v>
+        <v>0.711754068716094</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0</v>
+        <v>0.7970000000000002</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>0</v>
+        <v>0.009146341463414634</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>Canal Tradicional</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -25289,46 +25289,46 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>YOGU YOGU INDIVIDUAL</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>30002099</v>
+        <v>30000306</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>NECTAR WATTS TUTTIFLLA SIXPACK 30X200ML</t>
+          <t>YOGU YOGU DAMASCO 30X200GR</t>
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>31</v>
+        <v>2.2004</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>31.104</v>
+        <v>1.776</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>31.104</v>
+        <v>1.728</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.1039999999999992</v>
+        <v>-0.4244000000000001</v>
       </c>
       <c r="K154" s="3" t="n">
-        <v>1.003354838709677</v>
+        <v>0.8071259770950736</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>0.4244000000000001</v>
       </c>
       <c r="M154" s="3" t="n">
-        <v>0</v>
+        <v>0.02702702702702703</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ccu</t>
+          <t>Canal Tradicional</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -25338,40 +25338,40 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NECTAR WATTS REGULAR INDIVIDUAL</t>
+          <t>YOGU YOGU INDIVIDUAL</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>30000257</v>
+        <v>30000308</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NECTAR WATTS MZNA SIXPACK 30X200ML</t>
+          <t>YOGU YOGU VAINILLA 30X200GR</t>
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>13</v>
+        <v>1.8164</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>13.824</v>
+        <v>0.876</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>13.824</v>
+        <v>0.858</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.8239999999999998</v>
+        <v>-0.9404</v>
       </c>
       <c r="K155" s="3" t="n">
-        <v>1.063384615384615</v>
+        <v>0.4822726271746312</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>0.9404</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>0</v>
+        <v>0.0136986301369863</v>
       </c>
     </row>
     <row r="156">
